--- a/data/嘉盛物料映射汇总表.xlsx
+++ b/data/嘉盛物料映射汇总表.xlsx
@@ -5,17 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Winloud\Desktop\嘉盛物料映射汇总脚本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Winloud\Desktop\嘉盛物料映射工具_v1.1.0_编码规范修正版\嘉盛物料映射工具\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE9C3F9-2980-427F-B946-BA07A9E585D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9AAE01-7968-4B2B-A993-E68658E7DD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="1" r:id="rId1"/>
     <sheet name="公共物料" sheetId="2" r:id="rId2"/>
+    <sheet name="扩展物料" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">汇总!$A$1:$Z$275</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2516" uniqueCount="917">
   <si>
     <t>序号</t>
   </si>
@@ -2774,15 +2778,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>型号缺失</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>客供件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>已定义</t>
+    <t>已扩展</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工核对</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12732,8 +12736,9 @@
       <c r="J188" t="s">
         <v>657</v>
       </c>
-      <c r="L188" s="2" t="s">
-        <v>915</v>
+      <c r="L188" s="2"/>
+      <c r="M188" s="2" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="189" spans="1:24" x14ac:dyDescent="0.25">
@@ -12764,8 +12769,9 @@
       <c r="J189" t="s">
         <v>657</v>
       </c>
-      <c r="L189" s="2" t="s">
-        <v>915</v>
+      <c r="L189" s="2"/>
+      <c r="M189" s="2" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="190" spans="1:24" x14ac:dyDescent="0.25">
@@ -12796,8 +12802,9 @@
       <c r="J190" t="s">
         <v>657</v>
       </c>
-      <c r="L190" s="2" t="s">
-        <v>915</v>
+      <c r="L190" s="2"/>
+      <c r="M190" s="2" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="191" spans="1:24" x14ac:dyDescent="0.25">
@@ -12854,8 +12861,11 @@
       <c r="J192" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M192" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>20</v>
       </c>
@@ -12883,8 +12893,11 @@
       <c r="J193" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M193" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>24</v>
       </c>
@@ -12912,8 +12925,11 @@
       <c r="J194" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M194" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1</v>
       </c>
@@ -12939,7 +12955,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>16</v>
       </c>
@@ -12967,8 +12983,11 @@
       <c r="J196" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M196" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>20</v>
       </c>
@@ -12996,8 +13015,11 @@
       <c r="J197" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M197" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>24</v>
       </c>
@@ -13025,8 +13047,11 @@
       <c r="J198" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M198" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>20</v>
       </c>
@@ -13054,8 +13079,11 @@
       <c r="J199" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M199" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>1</v>
       </c>
@@ -13081,7 +13109,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>16</v>
       </c>
@@ -13109,8 +13137,11 @@
       <c r="J201" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M201" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>20</v>
       </c>
@@ -13138,8 +13169,11 @@
       <c r="J202" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M202" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>16</v>
       </c>
@@ -13167,8 +13201,11 @@
       <c r="J203" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M203" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>18</v>
       </c>
@@ -13194,7 +13231,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>20</v>
       </c>
@@ -13222,8 +13259,11 @@
       <c r="J205" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M205" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>21</v>
       </c>
@@ -13251,8 +13291,11 @@
       <c r="J206" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M206" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>1</v>
       </c>
@@ -13278,7 +13321,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>16</v>
       </c>
@@ -13306,8 +13349,11 @@
       <c r="J208" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M208" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>21</v>
       </c>
@@ -13335,8 +13381,11 @@
       <c r="J209" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M209" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>25</v>
       </c>
@@ -13364,8 +13413,11 @@
       <c r="J210" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M210" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>16</v>
       </c>
@@ -13393,8 +13445,11 @@
       <c r="J211" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M211" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1</v>
       </c>
@@ -13420,7 +13475,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>16</v>
       </c>
@@ -13448,8 +13503,11 @@
       <c r="J213" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M213" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>11</v>
       </c>
@@ -13478,7 +13536,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>14</v>
       </c>
@@ -13507,7 +13565,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>11</v>
       </c>
@@ -13536,7 +13594,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>14</v>
       </c>
@@ -13565,7 +13623,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1</v>
       </c>
@@ -13591,7 +13649,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>11</v>
       </c>
@@ -13620,7 +13678,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>15</v>
       </c>
@@ -13649,7 +13707,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>14</v>
       </c>
@@ -13678,7 +13736,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>16</v>
       </c>
@@ -13707,7 +13765,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>19</v>
       </c>
@@ -13736,7 +13794,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>16</v>
       </c>
@@ -13765,7 +13823,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>19</v>
       </c>
@@ -13794,7 +13852,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>23</v>
       </c>
@@ -13823,7 +13881,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>16</v>
       </c>
@@ -13852,7 +13910,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>19</v>
       </c>
@@ -13881,7 +13939,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>23</v>
       </c>
@@ -13910,7 +13968,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>11</v>
       </c>
@@ -13938,8 +13996,11 @@
       <c r="J230" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M230" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>3</v>
       </c>
@@ -13968,7 +14029,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>15</v>
       </c>
@@ -13996,8 +14057,11 @@
       <c r="J232" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M232" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>13</v>
       </c>
@@ -14023,7 +14087,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>15</v>
       </c>
@@ -14052,7 +14116,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1</v>
       </c>
@@ -14078,7 +14142,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1</v>
       </c>
@@ -14104,7 +14168,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
         <v>769</v>
       </c>
@@ -14130,7 +14194,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>69</v>
       </c>
@@ -14159,7 +14223,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>773</v>
       </c>
@@ -14185,7 +14249,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
         <v>777</v>
       </c>
@@ -14211,7 +14275,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
         <v>779</v>
       </c>
@@ -14237,7 +14301,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>69</v>
       </c>
@@ -14266,7 +14330,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>69</v>
       </c>
@@ -14295,7 +14359,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>22</v>
       </c>
@@ -14323,8 +14387,11 @@
       <c r="J244" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M244" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>3</v>
       </c>
@@ -14349,11 +14416,12 @@
       <c r="J245" t="s">
         <v>722</v>
       </c>
-      <c r="L245" s="2" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L245" s="2"/>
+      <c r="M245" s="2" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>2</v>
       </c>
@@ -14379,7 +14447,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>16</v>
       </c>
@@ -14408,7 +14476,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>22</v>
       </c>
@@ -14437,7 +14505,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>28</v>
       </c>
@@ -14466,7 +14534,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>16</v>
       </c>
@@ -14495,7 +14563,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>23</v>
       </c>
@@ -14524,7 +14592,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>30</v>
       </c>
@@ -14553,7 +14621,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>16</v>
       </c>
@@ -14582,7 +14650,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>23</v>
       </c>
@@ -14611,7 +14679,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>16</v>
       </c>
@@ -14640,7 +14708,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>16</v>
       </c>
@@ -14669,7 +14737,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>22</v>
       </c>
@@ -14698,7 +14766,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>28</v>
       </c>
@@ -14727,7 +14795,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>74</v>
       </c>
@@ -14753,7 +14821,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>19</v>
       </c>
@@ -14781,8 +14849,11 @@
       <c r="J260" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M260" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>22</v>
       </c>
@@ -14810,8 +14881,11 @@
       <c r="J261" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="M261" s="2" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>16</v>
       </c>
@@ -14840,7 +14914,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1</v>
       </c>
@@ -14866,7 +14940,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>1</v>
       </c>
@@ -14892,7 +14966,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>11</v>
       </c>
@@ -14921,7 +14995,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>14</v>
       </c>
@@ -14950,7 +15024,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>11</v>
       </c>
@@ -14979,7 +15053,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>14</v>
       </c>
@@ -15008,7 +15082,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>18</v>
       </c>
@@ -15037,7 +15111,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1</v>
       </c>
@@ -15063,7 +15137,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>22</v>
       </c>
@@ -15092,7 +15166,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>48</v>
       </c>
@@ -15206,6 +15280,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z275" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15213,7 +15288,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.54296875" customWidth="1"/>
@@ -15307,13 +15382,15 @@
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
-        <v>872</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>873</v>
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>901</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -15322,15 +15399,11 @@
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="6">
-        <v>1</v>
-      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="6">
+        <v>1547690000</v>
+      </c>
+      <c r="N2" s="6"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -15343,13 +15416,15 @@
       <c r="X2" s="5"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>875</v>
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>902</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -15358,15 +15433,11 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6">
+        <v>2428560000</v>
+      </c>
+      <c r="N3" s="6"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
@@ -15379,13 +15450,15 @@
       <c r="X3" s="5"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>876</v>
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>904</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -15394,15 +15467,11 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6">
+        <v>1527730000</v>
+      </c>
+      <c r="N4" s="6"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
@@ -15415,13 +15484,15 @@
       <c r="X4" s="5"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>877</v>
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
+        <v>905</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>906</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -15430,15 +15501,11 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="6">
+        <v>2428510000</v>
+      </c>
+      <c r="N5" s="6"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
@@ -15451,13 +15518,15 @@
       <c r="X5" s="5"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>878</v>
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>908</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -15466,15 +15535,11 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6">
+        <v>1547610000</v>
+      </c>
+      <c r="N6" s="6"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
@@ -15487,13 +15552,15 @@
       <c r="X6" s="5"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>879</v>
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>910</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -15502,15 +15569,11 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6">
+        <v>1129450000</v>
+      </c>
+      <c r="N7" s="6"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
@@ -15522,6 +15585,324 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
     </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FE38A3-B176-438B-888A-7BBBA1FF49C7}">
+  <dimension ref="A1:X25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="9.54296875" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" customWidth="1"/>
+    <col min="4" max="4" width="32.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" customWidth="1"/>
+    <col min="10" max="10" width="17.90625" customWidth="1"/>
+    <col min="12" max="12" width="13.54296875" customWidth="1"/>
+    <col min="13" max="13" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="6">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+    </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
@@ -15539,7 +15920,7 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>390</v>
@@ -15575,7 +15956,7 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>569</v>
@@ -15611,7 +15992,7 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>529</v>
@@ -15647,7 +16028,7 @@
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>36</v>
@@ -15683,7 +16064,7 @@
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>322</v>
@@ -15719,7 +16100,7 @@
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>530</v>
@@ -15755,7 +16136,7 @@
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>38</v>
@@ -15791,7 +16172,7 @@
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>194</v>
@@ -15827,7 +16208,7 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>32</v>
@@ -15863,7 +16244,7 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>320</v>
@@ -15899,7 +16280,7 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M18" s="6">
         <v>5961</v>
@@ -15935,7 +16316,7 @@
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M19" s="6">
         <v>5963</v>
@@ -15971,7 +16352,7 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>146</v>
@@ -16007,7 +16388,7 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>148</v>
@@ -16043,7 +16424,7 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>149</v>
@@ -16079,7 +16460,7 @@
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>30</v>
@@ -16102,11 +16483,9 @@
       <c r="A24" s="5"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7" t="s">
-        <v>900</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>901</v>
-      </c>
+        <v>911</v>
+      </c>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -16114,11 +16493,15 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="6">
-        <v>1547690000</v>
-      </c>
-      <c r="N24" s="6"/>
+      <c r="L24" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
@@ -16134,11 +16517,9 @@
       <c r="A25" s="5"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7" t="s">
-        <v>900</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>902</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -16146,11 +16527,15 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="6">
-        <v>2428560000</v>
-      </c>
-      <c r="N25" s="6"/>
+      <c r="L25" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
@@ -16162,202 +16547,6 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>904</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="6">
-        <v>1527730000</v>
-      </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7" t="s">
-        <v>905</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>906</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="6">
-        <v>2428510000</v>
-      </c>
-      <c r="N27" s="6"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
-      <c r="X27" s="5"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="6">
-        <v>1547610000</v>
-      </c>
-      <c r="N28" s="6"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
-      <c r="X28" s="5"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>910</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="6">
-        <v>1129450000</v>
-      </c>
-      <c r="N29" s="6"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
-      <c r="V29" s="5"/>
-      <c r="W29" s="5"/>
-      <c r="X29" s="5"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-      <c r="U30" s="5"/>
-      <c r="V30" s="5"/>
-      <c r="W30" s="5"/>
-      <c r="X30" s="5"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7" t="s">
-        <v>912</v>
-      </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="M31" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="N31" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
-      <c r="V31" s="5"/>
-      <c r="W31" s="5"/>
-      <c r="X31" s="5"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
